--- a/examples/hide-first-sheet.xlsx
+++ b/examples/hide-first-sheet.xlsx
@@ -6,8 +6,8 @@
     <workbookView firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hidden" sheetId="1" r:id="rId1" state="hidden"/>
-    <sheet name="Visible" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="Hidden" state="hidden"/>
+    <sheet r:id="rId2" sheetId="2" name="Visible"/>
   </sheets>
   <definedNames/>
   <calcPr/>
